--- a/Action/Data/CSV/Platform2/PlatformData.xlsx
+++ b/Action/Data/CSV/Platform2/PlatformData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FFF20FB5-22DA-47B3-A7C9-1A1FFC309868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11AFD41E-3795-4157-9B67-7BD523BAB1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -977,13 +977,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16" width="5.625" customWidth="1"/>
+    <col min="1" max="17" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>420</v>
       </c>
       <c r="M1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N1">
         <v>0</v>
@@ -1035,8 +1035,11 @@
       <c r="P1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="Q1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>-210</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>200</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -1088,16 +1091,19 @@
       <c r="P2">
         <v>0</v>
       </c>
-      <c r="R2">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <f>A1+J1/2-J2/2</f>
         <v>-210</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <f>C1-L1/2-L2/2</f>
         <v>-510</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>-420</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>420</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -1149,16 +1155,19 @@
       <c r="P3">
         <v>0</v>
       </c>
-      <c r="R3">
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <f>A2-J2/2+J3/2</f>
         <v>-420</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <f>C2-L2/2-L3/2</f>
         <v>-820</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-10</v>
       </c>
@@ -1199,7 +1208,7 @@
         <v>400</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1210,16 +1219,19 @@
       <c r="P4">
         <v>0</v>
       </c>
-      <c r="R4">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <f>A3-J3/2+J4/2</f>
         <v>-10</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <f>C3-L3/2-L4/2</f>
         <v>-1230</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>450</v>
       </c>
@@ -1260,27 +1272,30 @@
         <v>100</v>
       </c>
       <c r="M5">
+        <v>-1</v>
+      </c>
+      <c r="N5">
         <v>450</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>120</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>-980</v>
       </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="R5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="S5">
         <f>A4+J4/2-J5/2</f>
         <v>450</v>
       </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T66" si="7">C4+L4/2+L5/2</f>
+      <c r="U5">
+        <f t="shared" ref="U5:U66" si="7">C4+L4/2+L5/2</f>
         <v>-980</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>450</v>
       </c>
@@ -1321,7 +1336,7 @@
         <v>420</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1332,16 +1347,19 @@
       <c r="P6">
         <v>0</v>
       </c>
-      <c r="R6">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <f>A5-J5/2+J6/2</f>
         <v>500</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <f t="shared" si="7"/>
         <v>-720</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1382,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1393,16 +1411,19 @@
       <c r="P7">
         <v>0</v>
       </c>
-      <c r="R7">
-        <f t="shared" ref="R7:R66" si="8">A6+J6/2+J7/2</f>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S7:S66" si="8">A6+J6/2+J7/2</f>
         <v>560</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <f t="shared" si="7"/>
         <v>-500</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1443,7 +1464,7 @@
         <v>20</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1454,16 +1475,19 @@
       <c r="P8">
         <v>0</v>
       </c>
-      <c r="R8">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1504,7 +1528,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1515,16 +1539,19 @@
       <c r="P9">
         <v>0</v>
       </c>
-      <c r="R9">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1565,7 +1592,7 @@
         <v>20</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1576,16 +1603,19 @@
       <c r="P10">
         <v>0</v>
       </c>
-      <c r="R10">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>0</v>
       </c>
@@ -1626,7 +1656,7 @@
         <v>20</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1637,16 +1667,19 @@
       <c r="P11">
         <v>0</v>
       </c>
-      <c r="R11">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>0</v>
       </c>
@@ -1687,7 +1720,7 @@
         <v>20</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1698,16 +1731,19 @@
       <c r="P12">
         <v>0</v>
       </c>
-      <c r="R12">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>0</v>
       </c>
@@ -1748,7 +1784,7 @@
         <v>20</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1759,16 +1795,19 @@
       <c r="P13">
         <v>0</v>
       </c>
-      <c r="R13">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>0</v>
       </c>
@@ -1809,7 +1848,7 @@
         <v>20</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1820,16 +1859,19 @@
       <c r="P14">
         <v>0</v>
       </c>
-      <c r="R14">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>0</v>
       </c>
@@ -1870,7 +1912,7 @@
         <v>20</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1881,16 +1923,19 @@
       <c r="P15">
         <v>0</v>
       </c>
-      <c r="R15">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>0</v>
       </c>
@@ -1931,7 +1976,7 @@
         <v>20</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1942,16 +1987,19 @@
       <c r="P16">
         <v>0</v>
       </c>
-      <c r="R16">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>0</v>
       </c>
@@ -1992,7 +2040,7 @@
         <v>20</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2003,16 +2051,19 @@
       <c r="P17">
         <v>0</v>
       </c>
-      <c r="R17">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>0</v>
       </c>
@@ -2053,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2064,16 +2115,19 @@
       <c r="P18">
         <v>0</v>
       </c>
-      <c r="R18">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>0</v>
       </c>
@@ -2114,7 +2168,7 @@
         <v>20</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2125,16 +2179,19 @@
       <c r="P19">
         <v>0</v>
       </c>
-      <c r="R19">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>0</v>
       </c>
@@ -2175,7 +2232,7 @@
         <v>20</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2186,16 +2243,19 @@
       <c r="P20">
         <v>0</v>
       </c>
-      <c r="R20">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="S20">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>0</v>
       </c>
@@ -2236,7 +2296,7 @@
         <v>20</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2247,16 +2307,19 @@
       <c r="P21">
         <v>0</v>
       </c>
-      <c r="R21">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>0</v>
       </c>
@@ -2297,7 +2360,7 @@
         <v>20</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2308,16 +2371,19 @@
       <c r="P22">
         <v>0</v>
       </c>
-      <c r="R22">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>0</v>
       </c>
@@ -2358,7 +2424,7 @@
         <v>20</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2369,16 +2435,19 @@
       <c r="P23">
         <v>0</v>
       </c>
-      <c r="R23">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>0</v>
       </c>
@@ -2419,7 +2488,7 @@
         <v>20</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2430,16 +2499,19 @@
       <c r="P24">
         <v>0</v>
       </c>
-      <c r="R24">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>0</v>
       </c>
@@ -2480,7 +2552,7 @@
         <v>20</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -2491,16 +2563,19 @@
       <c r="P25">
         <v>0</v>
       </c>
-      <c r="R25">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>0</v>
       </c>
@@ -2541,7 +2616,7 @@
         <v>20</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -2552,16 +2627,19 @@
       <c r="P26">
         <v>0</v>
       </c>
-      <c r="R26">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="S26">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>0</v>
       </c>
@@ -2602,7 +2680,7 @@
         <v>20</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -2613,16 +2691,19 @@
       <c r="P27">
         <v>0</v>
       </c>
-      <c r="R27">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>0</v>
       </c>
@@ -2663,7 +2744,7 @@
         <v>20</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -2674,16 +2755,19 @@
       <c r="P28">
         <v>0</v>
       </c>
-      <c r="R28">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>0</v>
       </c>
@@ -2724,7 +2808,7 @@
         <v>20</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2735,16 +2819,19 @@
       <c r="P29">
         <v>0</v>
       </c>
-      <c r="R29">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="S29">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>0</v>
       </c>
@@ -2785,7 +2872,7 @@
         <v>20</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2796,16 +2883,19 @@
       <c r="P30">
         <v>0</v>
       </c>
-      <c r="R30">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>0</v>
       </c>
@@ -2846,7 +2936,7 @@
         <v>20</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -2857,16 +2947,19 @@
       <c r="P31">
         <v>0</v>
       </c>
-      <c r="R31">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>0</v>
       </c>
@@ -2907,7 +3000,7 @@
         <v>20</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -2918,16 +3011,19 @@
       <c r="P32">
         <v>0</v>
       </c>
-      <c r="R32">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="S32">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>0</v>
       </c>
@@ -2968,7 +3064,7 @@
         <v>20</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2979,16 +3075,19 @@
       <c r="P33">
         <v>0</v>
       </c>
-      <c r="R33">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>0</v>
       </c>
@@ -3029,7 +3128,7 @@
         <v>20</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -3040,16 +3139,19 @@
       <c r="P34">
         <v>0</v>
       </c>
-      <c r="R34">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="S34">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>0</v>
       </c>
@@ -3090,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -3101,16 +3203,19 @@
       <c r="P35">
         <v>0</v>
       </c>
-      <c r="R35">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>0</v>
       </c>
@@ -3151,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -3162,16 +3267,19 @@
       <c r="P36">
         <v>0</v>
       </c>
-      <c r="R36">
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="S36">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>0</v>
       </c>
@@ -3212,7 +3320,7 @@
         <v>20</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -3223,16 +3331,19 @@
       <c r="P37">
         <v>0</v>
       </c>
-      <c r="R37">
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T37">
+      <c r="U37">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>0</v>
       </c>
@@ -3273,7 +3384,7 @@
         <v>20</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -3284,16 +3395,19 @@
       <c r="P38">
         <v>0</v>
       </c>
-      <c r="R38">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="S38">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T38">
+      <c r="U38">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>0</v>
       </c>
@@ -3334,7 +3448,7 @@
         <v>20</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -3345,16 +3459,19 @@
       <c r="P39">
         <v>0</v>
       </c>
-      <c r="R39">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T39">
+      <c r="U39">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>0</v>
       </c>
@@ -3395,7 +3512,7 @@
         <v>20</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -3406,16 +3523,19 @@
       <c r="P40">
         <v>0</v>
       </c>
-      <c r="R40">
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>0</v>
       </c>
@@ -3456,7 +3576,7 @@
         <v>20</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -3467,16 +3587,19 @@
       <c r="P41">
         <v>0</v>
       </c>
-      <c r="R41">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T41">
+      <c r="U41">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>0</v>
       </c>
@@ -3517,7 +3640,7 @@
         <v>20</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -3528,16 +3651,19 @@
       <c r="P42">
         <v>0</v>
       </c>
-      <c r="R42">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T42">
+      <c r="U42">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>0</v>
       </c>
@@ -3578,7 +3704,7 @@
         <v>20</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -3589,16 +3715,19 @@
       <c r="P43">
         <v>0</v>
       </c>
-      <c r="R43">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T43">
+      <c r="U43">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>0</v>
       </c>
@@ -3639,7 +3768,7 @@
         <v>20</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -3650,16 +3779,19 @@
       <c r="P44">
         <v>0</v>
       </c>
-      <c r="R44">
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T44">
+      <c r="U44">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>0</v>
       </c>
@@ -3700,7 +3832,7 @@
         <v>20</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -3711,16 +3843,19 @@
       <c r="P45">
         <v>0</v>
       </c>
-      <c r="R45">
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T45">
+      <c r="U45">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>0</v>
       </c>
@@ -3761,7 +3896,7 @@
         <v>20</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -3772,16 +3907,19 @@
       <c r="P46">
         <v>0</v>
       </c>
-      <c r="R46">
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="S46">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>0</v>
       </c>
@@ -3822,7 +3960,7 @@
         <v>20</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N47">
         <v>0</v>
@@ -3833,16 +3971,19 @@
       <c r="P47">
         <v>0</v>
       </c>
-      <c r="R47">
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="S47">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T47">
+      <c r="U47">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>0</v>
       </c>
@@ -3883,7 +4024,7 @@
         <v>20</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N48">
         <v>0</v>
@@ -3894,16 +4035,19 @@
       <c r="P48">
         <v>0</v>
       </c>
-      <c r="R48">
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="S48">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T48">
+      <c r="U48">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>0</v>
       </c>
@@ -3944,7 +4088,7 @@
         <v>20</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -3955,16 +4099,19 @@
       <c r="P49">
         <v>0</v>
       </c>
-      <c r="R49">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T49">
+      <c r="U49">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>0</v>
       </c>
@@ -4005,7 +4152,7 @@
         <v>20</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -4016,16 +4163,19 @@
       <c r="P50">
         <v>0</v>
       </c>
-      <c r="R50">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="S50">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T50">
+      <c r="U50">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>0</v>
       </c>
@@ -4066,7 +4216,7 @@
         <v>20</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -4077,16 +4227,19 @@
       <c r="P51">
         <v>0</v>
       </c>
-      <c r="R51">
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="S51">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T51">
+      <c r="U51">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>0</v>
       </c>
@@ -4127,7 +4280,7 @@
         <v>20</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -4138,16 +4291,19 @@
       <c r="P52">
         <v>0</v>
       </c>
-      <c r="R52">
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="S52">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T52">
+      <c r="U52">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>0</v>
       </c>
@@ -4188,7 +4344,7 @@
         <v>20</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -4199,16 +4355,19 @@
       <c r="P53">
         <v>0</v>
       </c>
-      <c r="R53">
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>0</v>
       </c>
@@ -4249,7 +4408,7 @@
         <v>20</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -4260,16 +4419,19 @@
       <c r="P54">
         <v>0</v>
       </c>
-      <c r="R54">
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T54">
+      <c r="U54">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>0</v>
       </c>
@@ -4310,7 +4472,7 @@
         <v>20</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -4321,16 +4483,19 @@
       <c r="P55">
         <v>0</v>
       </c>
-      <c r="R55">
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="S55">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T55">
+      <c r="U55">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>0</v>
       </c>
@@ -4371,7 +4536,7 @@
         <v>20</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -4382,16 +4547,19 @@
       <c r="P56">
         <v>0</v>
       </c>
-      <c r="R56">
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>0</v>
       </c>
@@ -4432,7 +4600,7 @@
         <v>20</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -4443,16 +4611,19 @@
       <c r="P57">
         <v>0</v>
       </c>
-      <c r="R57">
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="S57">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T57">
+      <c r="U57">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>0</v>
       </c>
@@ -4493,7 +4664,7 @@
         <v>20</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -4504,16 +4675,19 @@
       <c r="P58">
         <v>0</v>
       </c>
-      <c r="R58">
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T58">
+      <c r="U58">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>0</v>
       </c>
@@ -4554,7 +4728,7 @@
         <v>20</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -4565,16 +4739,19 @@
       <c r="P59">
         <v>0</v>
       </c>
-      <c r="R59">
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T59">
+      <c r="U59">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>0</v>
       </c>
@@ -4615,7 +4792,7 @@
         <v>20</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -4626,16 +4803,19 @@
       <c r="P60">
         <v>0</v>
       </c>
-      <c r="R60">
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="S60">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T60">
+      <c r="U60">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>0</v>
       </c>
@@ -4676,7 +4856,7 @@
         <v>20</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -4687,16 +4867,19 @@
       <c r="P61">
         <v>0</v>
       </c>
-      <c r="R61">
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="S61">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T61">
+      <c r="U61">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>0</v>
       </c>
@@ -4737,7 +4920,7 @@
         <v>20</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -4748,16 +4931,19 @@
       <c r="P62">
         <v>0</v>
       </c>
-      <c r="R62">
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T62">
+      <c r="U62">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>0</v>
       </c>
@@ -4798,7 +4984,7 @@
         <v>20</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N63">
         <v>0</v>
@@ -4809,16 +4995,19 @@
       <c r="P63">
         <v>0</v>
       </c>
-      <c r="R63">
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="S63">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T63">
+      <c r="U63">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>0</v>
       </c>
@@ -4859,7 +5048,7 @@
         <v>20</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -4870,16 +5059,19 @@
       <c r="P64">
         <v>0</v>
       </c>
-      <c r="R64">
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T64">
+      <c r="U64">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>0</v>
       </c>
@@ -4920,7 +5112,7 @@
         <v>20</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -4931,16 +5123,19 @@
       <c r="P65">
         <v>0</v>
       </c>
-      <c r="R65">
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="S65">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T65">
+      <c r="U65">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>0</v>
       </c>
@@ -4981,7 +5176,7 @@
         <v>20</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -4992,16 +5187,19 @@
       <c r="P66">
         <v>0</v>
       </c>
-      <c r="R66">
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="S66">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="T66">
+      <c r="U66">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>0</v>
       </c>
@@ -5042,7 +5240,7 @@
         <v>20</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -5053,16 +5251,19 @@
       <c r="P67">
         <v>0</v>
       </c>
-      <c r="R67">
-        <f t="shared" ref="R67:R100" si="12">A66+J66/2+J67/2</f>
-        <v>20</v>
-      </c>
-      <c r="T67">
-        <f t="shared" ref="T67:T100" si="13">C66+L66/2+L67/2</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <f t="shared" ref="S67:S100" si="12">A66+J66/2+J67/2</f>
+        <v>20</v>
+      </c>
+      <c r="U67">
+        <f t="shared" ref="U67:U100" si="13">C66+L66/2+L67/2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>0</v>
       </c>
@@ -5103,7 +5304,7 @@
         <v>20</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -5114,16 +5315,19 @@
       <c r="P68">
         <v>0</v>
       </c>
-      <c r="R68">
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="S68">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T68">
+      <c r="U68">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>0</v>
       </c>
@@ -5164,7 +5368,7 @@
         <v>20</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -5175,16 +5379,19 @@
       <c r="P69">
         <v>0</v>
       </c>
-      <c r="R69">
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="S69">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T69">
+      <c r="U69">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>0</v>
       </c>
@@ -5225,7 +5432,7 @@
         <v>20</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N70">
         <v>0</v>
@@ -5236,16 +5443,19 @@
       <c r="P70">
         <v>0</v>
       </c>
-      <c r="R70">
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="S70">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T70">
+      <c r="U70">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>0</v>
       </c>
@@ -5286,7 +5496,7 @@
         <v>20</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N71">
         <v>0</v>
@@ -5297,16 +5507,19 @@
       <c r="P71">
         <v>0</v>
       </c>
-      <c r="R71">
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="S71">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T71">
+      <c r="U71">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>0</v>
       </c>
@@ -5347,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -5358,16 +5571,19 @@
       <c r="P72">
         <v>0</v>
       </c>
-      <c r="R72">
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="S72">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T72">
+      <c r="U72">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>0</v>
       </c>
@@ -5408,7 +5624,7 @@
         <v>20</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5419,16 +5635,19 @@
       <c r="P73">
         <v>0</v>
       </c>
-      <c r="R73">
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="S73">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T73">
+      <c r="U73">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>0</v>
       </c>
@@ -5469,7 +5688,7 @@
         <v>20</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -5480,16 +5699,19 @@
       <c r="P74">
         <v>0</v>
       </c>
-      <c r="R74">
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="S74">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T74">
+      <c r="U74">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>0</v>
       </c>
@@ -5530,7 +5752,7 @@
         <v>20</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -5541,16 +5763,19 @@
       <c r="P75">
         <v>0</v>
       </c>
-      <c r="R75">
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="S75">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T75">
+      <c r="U75">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>0</v>
       </c>
@@ -5591,7 +5816,7 @@
         <v>20</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5602,16 +5827,19 @@
       <c r="P76">
         <v>0</v>
       </c>
-      <c r="R76">
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="S76">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T76">
+      <c r="U76">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>0</v>
       </c>
@@ -5652,7 +5880,7 @@
         <v>20</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -5663,16 +5891,19 @@
       <c r="P77">
         <v>0</v>
       </c>
-      <c r="R77">
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="S77">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T77">
+      <c r="U77">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>0</v>
       </c>
@@ -5713,7 +5944,7 @@
         <v>20</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N78">
         <v>0</v>
@@ -5724,16 +5955,19 @@
       <c r="P78">
         <v>0</v>
       </c>
-      <c r="R78">
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="S78">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T78">
+      <c r="U78">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>0</v>
       </c>
@@ -5774,7 +6008,7 @@
         <v>20</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -5785,16 +6019,19 @@
       <c r="P79">
         <v>0</v>
       </c>
-      <c r="R79">
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="S79">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T79">
+      <c r="U79">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>0</v>
       </c>
@@ -5835,7 +6072,7 @@
         <v>20</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -5846,16 +6083,19 @@
       <c r="P80">
         <v>0</v>
       </c>
-      <c r="R80">
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="S80">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T80">
+      <c r="U80">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>0</v>
       </c>
@@ -5896,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N81">
         <v>0</v>
@@ -5907,16 +6147,19 @@
       <c r="P81">
         <v>0</v>
       </c>
-      <c r="R81">
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="S81">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T81">
+      <c r="U81">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>0</v>
       </c>
@@ -5957,7 +6200,7 @@
         <v>20</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -5968,16 +6211,19 @@
       <c r="P82">
         <v>0</v>
       </c>
-      <c r="R82">
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="S82">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T82">
+      <c r="U82">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>0</v>
       </c>
@@ -6018,7 +6264,7 @@
         <v>20</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -6029,16 +6275,19 @@
       <c r="P83">
         <v>0</v>
       </c>
-      <c r="R83">
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="S83">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T83">
+      <c r="U83">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>0</v>
       </c>
@@ -6079,7 +6328,7 @@
         <v>20</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N84">
         <v>0</v>
@@ -6090,16 +6339,19 @@
       <c r="P84">
         <v>0</v>
       </c>
-      <c r="R84">
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="S84">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T84">
+      <c r="U84">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>0</v>
       </c>
@@ -6140,7 +6392,7 @@
         <v>20</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N85">
         <v>0</v>
@@ -6151,16 +6403,19 @@
       <c r="P85">
         <v>0</v>
       </c>
-      <c r="R85">
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="S85">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T85">
+      <c r="U85">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>0</v>
       </c>
@@ -6201,7 +6456,7 @@
         <v>20</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N86">
         <v>0</v>
@@ -6212,16 +6467,19 @@
       <c r="P86">
         <v>0</v>
       </c>
-      <c r="R86">
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="S86">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T86">
+      <c r="U86">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>0</v>
       </c>
@@ -6262,7 +6520,7 @@
         <v>20</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N87">
         <v>0</v>
@@ -6273,16 +6531,19 @@
       <c r="P87">
         <v>0</v>
       </c>
-      <c r="R87">
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="S87">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T87">
+      <c r="U87">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>0</v>
       </c>
@@ -6323,7 +6584,7 @@
         <v>20</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N88">
         <v>0</v>
@@ -6334,16 +6595,19 @@
       <c r="P88">
         <v>0</v>
       </c>
-      <c r="R88">
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="S88">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T88">
+      <c r="U88">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>0</v>
       </c>
@@ -6384,7 +6648,7 @@
         <v>20</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6395,16 +6659,19 @@
       <c r="P89">
         <v>0</v>
       </c>
-      <c r="R89">
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="S89">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T89">
+      <c r="U89">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>0</v>
       </c>
@@ -6445,7 +6712,7 @@
         <v>20</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N90">
         <v>0</v>
@@ -6456,16 +6723,19 @@
       <c r="P90">
         <v>0</v>
       </c>
-      <c r="R90">
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="S90">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T90">
+      <c r="U90">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>0</v>
       </c>
@@ -6506,7 +6776,7 @@
         <v>20</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -6517,16 +6787,19 @@
       <c r="P91">
         <v>0</v>
       </c>
-      <c r="R91">
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="S91">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T91">
+      <c r="U91">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>0</v>
       </c>
@@ -6567,7 +6840,7 @@
         <v>20</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N92">
         <v>0</v>
@@ -6578,16 +6851,19 @@
       <c r="P92">
         <v>0</v>
       </c>
-      <c r="R92">
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="S92">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T92">
+      <c r="U92">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>0</v>
       </c>
@@ -6628,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N93">
         <v>0</v>
@@ -6639,16 +6915,19 @@
       <c r="P93">
         <v>0</v>
       </c>
-      <c r="R93">
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="S93">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T93">
+      <c r="U93">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>0</v>
       </c>
@@ -6689,7 +6968,7 @@
         <v>20</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N94">
         <v>0</v>
@@ -6700,16 +6979,19 @@
       <c r="P94">
         <v>0</v>
       </c>
-      <c r="R94">
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="S94">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T94">
+      <c r="U94">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>0</v>
       </c>
@@ -6750,7 +7032,7 @@
         <v>20</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -6761,16 +7043,19 @@
       <c r="P95">
         <v>0</v>
       </c>
-      <c r="R95">
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="S95">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T95">
+      <c r="U95">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>0</v>
       </c>
@@ -6811,7 +7096,7 @@
         <v>20</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N96">
         <v>0</v>
@@ -6822,16 +7107,19 @@
       <c r="P96">
         <v>0</v>
       </c>
-      <c r="R96">
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="S96">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T96">
+      <c r="U96">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>0</v>
       </c>
@@ -6872,7 +7160,7 @@
         <v>20</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N97">
         <v>0</v>
@@ -6883,16 +7171,19 @@
       <c r="P97">
         <v>0</v>
       </c>
-      <c r="R97">
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="S97">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T97">
+      <c r="U97">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0</v>
       </c>
@@ -6933,7 +7224,7 @@
         <v>20</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N98">
         <v>0</v>
@@ -6944,16 +7235,19 @@
       <c r="P98">
         <v>0</v>
       </c>
-      <c r="R98">
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="S98">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T98">
+      <c r="U98">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0</v>
       </c>
@@ -6994,7 +7288,7 @@
         <v>20</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N99">
         <v>0</v>
@@ -7005,16 +7299,19 @@
       <c r="P99">
         <v>0</v>
       </c>
-      <c r="R99">
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="S99">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T99">
+      <c r="U99">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0</v>
       </c>
@@ -7055,7 +7352,7 @@
         <v>20</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N100">
         <v>0</v>
@@ -7066,11 +7363,14 @@
       <c r="P100">
         <v>0</v>
       </c>
-      <c r="R100">
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="S100">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="T100">
+      <c r="U100">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
